--- a/Australia/data_raw/643201.xlsx
+++ b/Australia/data_raw/643201.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\Excelerator\XmlTransform\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\Dissemination\ausstats\RPPIPublicationCurrent\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A2126C-D08B-42D6-943B-EAD00F0F0827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11490" windowHeight="7320"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -17,143 +18,143 @@
     <sheet name="Enquiries" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="A83728603C">Data1!$B$1:$B$10,Data1!$B$11:$B$68</definedName>
-    <definedName name="A83728603C_Data">Data1!$B$11:$B$68</definedName>
-    <definedName name="A83728603C_Latest">Data1!$B$68</definedName>
-    <definedName name="A83728604F">Data1!$K$1:$K$10,Data1!$K$11:$K$68</definedName>
-    <definedName name="A83728604F_Data">Data1!$K$11:$K$68</definedName>
-    <definedName name="A83728604F_Latest">Data1!$K$68</definedName>
-    <definedName name="A83728605J">Data1!$AL$1:$AL$10,Data1!$AL$11:$AL$68</definedName>
-    <definedName name="A83728605J_Data">Data1!$AL$11:$AL$68</definedName>
-    <definedName name="A83728605J_Latest">Data1!$AL$68</definedName>
-    <definedName name="A83728606K">Data1!$T$1:$T$10,Data1!$T$11:$T$68</definedName>
-    <definedName name="A83728606K_Data">Data1!$T$11:$T$68</definedName>
-    <definedName name="A83728606K_Latest">Data1!$T$68</definedName>
-    <definedName name="A83728607L">Data1!$AC$1:$AC$10,Data1!$AC$11:$AC$68</definedName>
-    <definedName name="A83728607L_Data">Data1!$AC$11:$AC$68</definedName>
-    <definedName name="A83728607L_Latest">Data1!$AC$68</definedName>
-    <definedName name="A83728608R">Data1!$C$1:$C$10,Data1!$C$11:$C$68</definedName>
-    <definedName name="A83728608R_Data">Data1!$C$11:$C$68</definedName>
-    <definedName name="A83728608R_Latest">Data1!$C$68</definedName>
-    <definedName name="A83728609T">Data1!$L$1:$L$10,Data1!$L$11:$L$68</definedName>
-    <definedName name="A83728609T_Data">Data1!$L$11:$L$68</definedName>
-    <definedName name="A83728609T_Latest">Data1!$L$68</definedName>
-    <definedName name="A83728610A">Data1!$AM$1:$AM$10,Data1!$AM$11:$AM$68</definedName>
-    <definedName name="A83728610A_Data">Data1!$AM$11:$AM$68</definedName>
-    <definedName name="A83728610A_Latest">Data1!$AM$68</definedName>
-    <definedName name="A83728611C">Data1!$U$1:$U$10,Data1!$U$11:$U$68</definedName>
-    <definedName name="A83728611C_Data">Data1!$U$11:$U$68</definedName>
-    <definedName name="A83728611C_Latest">Data1!$U$68</definedName>
-    <definedName name="A83728612F">Data1!$AD$1:$AD$10,Data1!$AD$11:$AD$68</definedName>
-    <definedName name="A83728612F_Data">Data1!$AD$11:$AD$68</definedName>
-    <definedName name="A83728612F_Latest">Data1!$AD$68</definedName>
-    <definedName name="A83728613J">Data1!$D$1:$D$10,Data1!$D$11:$D$68</definedName>
-    <definedName name="A83728613J_Data">Data1!$D$11:$D$68</definedName>
-    <definedName name="A83728613J_Latest">Data1!$D$68</definedName>
-    <definedName name="A83728614K">Data1!$M$1:$M$10,Data1!$M$11:$M$68</definedName>
-    <definedName name="A83728614K_Data">Data1!$M$11:$M$68</definedName>
-    <definedName name="A83728614K_Latest">Data1!$M$68</definedName>
-    <definedName name="A83728615L">Data1!$AN$1:$AN$10,Data1!$AN$11:$AN$68</definedName>
-    <definedName name="A83728615L_Data">Data1!$AN$11:$AN$68</definedName>
-    <definedName name="A83728615L_Latest">Data1!$AN$68</definedName>
-    <definedName name="A83728616R">Data1!$V$1:$V$10,Data1!$V$11:$V$68</definedName>
-    <definedName name="A83728616R_Data">Data1!$V$11:$V$68</definedName>
-    <definedName name="A83728616R_Latest">Data1!$V$68</definedName>
-    <definedName name="A83728617T">Data1!$AE$1:$AE$10,Data1!$AE$11:$AE$68</definedName>
-    <definedName name="A83728617T_Data">Data1!$AE$11:$AE$68</definedName>
-    <definedName name="A83728617T_Latest">Data1!$AE$68</definedName>
-    <definedName name="A83728618V">Data1!$E$1:$E$10,Data1!$E$11:$E$68</definedName>
-    <definedName name="A83728618V_Data">Data1!$E$11:$E$68</definedName>
-    <definedName name="A83728618V_Latest">Data1!$E$68</definedName>
-    <definedName name="A83728619W">Data1!$N$1:$N$10,Data1!$N$11:$N$68</definedName>
-    <definedName name="A83728619W_Data">Data1!$N$11:$N$68</definedName>
-    <definedName name="A83728619W_Latest">Data1!$N$68</definedName>
-    <definedName name="A83728620F">Data1!$AO$1:$AO$10,Data1!$AO$11:$AO$68</definedName>
-    <definedName name="A83728620F_Data">Data1!$AO$11:$AO$68</definedName>
-    <definedName name="A83728620F_Latest">Data1!$AO$68</definedName>
-    <definedName name="A83728621J">Data1!$W$1:$W$10,Data1!$W$11:$W$68</definedName>
-    <definedName name="A83728621J_Data">Data1!$W$11:$W$68</definedName>
-    <definedName name="A83728621J_Latest">Data1!$W$68</definedName>
-    <definedName name="A83728622K">Data1!$AF$1:$AF$10,Data1!$AF$11:$AF$68</definedName>
-    <definedName name="A83728622K_Data">Data1!$AF$11:$AF$68</definedName>
-    <definedName name="A83728622K_Latest">Data1!$AF$68</definedName>
-    <definedName name="A83728623L">Data1!$F$1:$F$10,Data1!$F$11:$F$68</definedName>
-    <definedName name="A83728623L_Data">Data1!$F$11:$F$68</definedName>
-    <definedName name="A83728623L_Latest">Data1!$F$68</definedName>
-    <definedName name="A83728624R">Data1!$O$1:$O$10,Data1!$O$11:$O$68</definedName>
-    <definedName name="A83728624R_Data">Data1!$O$11:$O$68</definedName>
-    <definedName name="A83728624R_Latest">Data1!$O$68</definedName>
-    <definedName name="A83728625T">Data1!$AP$1:$AP$10,Data1!$AP$11:$AP$68</definedName>
-    <definedName name="A83728625T_Data">Data1!$AP$11:$AP$68</definedName>
-    <definedName name="A83728625T_Latest">Data1!$AP$68</definedName>
-    <definedName name="A83728626V">Data1!$X$1:$X$10,Data1!$X$11:$X$68</definedName>
-    <definedName name="A83728626V_Data">Data1!$X$11:$X$68</definedName>
-    <definedName name="A83728626V_Latest">Data1!$X$68</definedName>
-    <definedName name="A83728627W">Data1!$AG$1:$AG$10,Data1!$AG$11:$AG$68</definedName>
-    <definedName name="A83728627W_Data">Data1!$AG$11:$AG$68</definedName>
-    <definedName name="A83728627W_Latest">Data1!$AG$68</definedName>
-    <definedName name="A83728628X">Data1!$G$1:$G$10,Data1!$G$11:$G$68</definedName>
-    <definedName name="A83728628X_Data">Data1!$G$11:$G$68</definedName>
-    <definedName name="A83728628X_Latest">Data1!$G$68</definedName>
-    <definedName name="A83728629A">Data1!$P$1:$P$10,Data1!$P$11:$P$68</definedName>
-    <definedName name="A83728629A_Data">Data1!$P$11:$P$68</definedName>
-    <definedName name="A83728629A_Latest">Data1!$P$68</definedName>
-    <definedName name="A83728630K">Data1!$AQ$1:$AQ$10,Data1!$AQ$11:$AQ$68</definedName>
-    <definedName name="A83728630K_Data">Data1!$AQ$11:$AQ$68</definedName>
-    <definedName name="A83728630K_Latest">Data1!$AQ$68</definedName>
-    <definedName name="A83728631L">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$68</definedName>
-    <definedName name="A83728631L_Data">Data1!$Y$11:$Y$68</definedName>
-    <definedName name="A83728631L_Latest">Data1!$Y$68</definedName>
-    <definedName name="A83728632R">Data1!$AH$1:$AH$10,Data1!$AH$11:$AH$68</definedName>
-    <definedName name="A83728632R_Data">Data1!$AH$11:$AH$68</definedName>
-    <definedName name="A83728632R_Latest">Data1!$AH$68</definedName>
-    <definedName name="A83728633T">Data1!$H$1:$H$10,Data1!$H$11:$H$68</definedName>
-    <definedName name="A83728633T_Data">Data1!$H$11:$H$68</definedName>
-    <definedName name="A83728633T_Latest">Data1!$H$68</definedName>
-    <definedName name="A83728634V">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$68</definedName>
-    <definedName name="A83728634V_Data">Data1!$Q$11:$Q$68</definedName>
-    <definedName name="A83728634V_Latest">Data1!$Q$68</definedName>
-    <definedName name="A83728635W">Data1!$AR$1:$AR$10,Data1!$AR$11:$AR$68</definedName>
-    <definedName name="A83728635W_Data">Data1!$AR$11:$AR$68</definedName>
-    <definedName name="A83728635W_Latest">Data1!$AR$68</definedName>
-    <definedName name="A83728636X">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$68</definedName>
-    <definedName name="A83728636X_Data">Data1!$Z$11:$Z$68</definedName>
-    <definedName name="A83728636X_Latest">Data1!$Z$68</definedName>
-    <definedName name="A83728637A">Data1!$AI$1:$AI$10,Data1!$AI$11:$AI$68</definedName>
-    <definedName name="A83728637A_Data">Data1!$AI$11:$AI$68</definedName>
-    <definedName name="A83728637A_Latest">Data1!$AI$68</definedName>
-    <definedName name="A83728638C">Data1!$I$1:$I$10,Data1!$I$11:$I$68</definedName>
-    <definedName name="A83728638C_Data">Data1!$I$11:$I$68</definedName>
-    <definedName name="A83728638C_Latest">Data1!$I$68</definedName>
-    <definedName name="A83728639F">Data1!$R$1:$R$10,Data1!$R$11:$R$68</definedName>
-    <definedName name="A83728639F_Data">Data1!$R$11:$R$68</definedName>
-    <definedName name="A83728639F_Latest">Data1!$R$68</definedName>
-    <definedName name="A83728640R">Data1!$AS$1:$AS$10,Data1!$AS$11:$AS$68</definedName>
-    <definedName name="A83728640R_Data">Data1!$AS$11:$AS$68</definedName>
-    <definedName name="A83728640R_Latest">Data1!$AS$68</definedName>
-    <definedName name="A83728641T">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$68</definedName>
-    <definedName name="A83728641T_Data">Data1!$AA$11:$AA$68</definedName>
-    <definedName name="A83728641T_Latest">Data1!$AA$68</definedName>
-    <definedName name="A83728642V">Data1!$AJ$1:$AJ$10,Data1!$AJ$11:$AJ$68</definedName>
-    <definedName name="A83728642V_Data">Data1!$AJ$11:$AJ$68</definedName>
-    <definedName name="A83728642V_Latest">Data1!$AJ$68</definedName>
-    <definedName name="A83728643W">Data1!$J$1:$J$10,Data1!$J$11:$J$68</definedName>
-    <definedName name="A83728643W_Data">Data1!$J$11:$J$68</definedName>
-    <definedName name="A83728643W_Latest">Data1!$J$68</definedName>
-    <definedName name="A83728644X">Data1!$S$1:$S$10,Data1!$S$11:$S$68</definedName>
-    <definedName name="A83728644X_Data">Data1!$S$11:$S$68</definedName>
-    <definedName name="A83728644X_Latest">Data1!$S$68</definedName>
-    <definedName name="A83728645A">Data1!$AT$1:$AT$10,Data1!$AT$11:$AT$68</definedName>
-    <definedName name="A83728645A_Data">Data1!$AT$11:$AT$68</definedName>
-    <definedName name="A83728645A_Latest">Data1!$AT$68</definedName>
-    <definedName name="A83728646C">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$68</definedName>
-    <definedName name="A83728646C_Data">Data1!$AB$11:$AB$68</definedName>
-    <definedName name="A83728646C_Latest">Data1!$AB$68</definedName>
-    <definedName name="A83728647F">Data1!$AK$1:$AK$10,Data1!$AK$11:$AK$68</definedName>
-    <definedName name="A83728647F_Data">Data1!$AK$11:$AK$68</definedName>
-    <definedName name="A83728647F_Latest">Data1!$AK$68</definedName>
-    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$68</definedName>
-    <definedName name="Date_Range_Data">Data1!$A$11:$A$68</definedName>
+    <definedName name="A83728603C">Data1!$B$1:$B$10,Data1!$B$11:$B$69</definedName>
+    <definedName name="A83728603C_Data">Data1!$B$11:$B$69</definedName>
+    <definedName name="A83728603C_Latest">Data1!$B$69</definedName>
+    <definedName name="A83728604F">Data1!$K$1:$K$10,Data1!$K$11:$K$69</definedName>
+    <definedName name="A83728604F_Data">Data1!$K$11:$K$69</definedName>
+    <definedName name="A83728604F_Latest">Data1!$K$69</definedName>
+    <definedName name="A83728605J">Data1!$AL$1:$AL$10,Data1!$AL$11:$AL$69</definedName>
+    <definedName name="A83728605J_Data">Data1!$AL$11:$AL$69</definedName>
+    <definedName name="A83728605J_Latest">Data1!$AL$69</definedName>
+    <definedName name="A83728606K">Data1!$T$1:$T$10,Data1!$T$11:$T$69</definedName>
+    <definedName name="A83728606K_Data">Data1!$T$11:$T$69</definedName>
+    <definedName name="A83728606K_Latest">Data1!$T$69</definedName>
+    <definedName name="A83728607L">Data1!$AC$1:$AC$10,Data1!$AC$11:$AC$69</definedName>
+    <definedName name="A83728607L_Data">Data1!$AC$11:$AC$69</definedName>
+    <definedName name="A83728607L_Latest">Data1!$AC$69</definedName>
+    <definedName name="A83728608R">Data1!$C$1:$C$10,Data1!$C$11:$C$69</definedName>
+    <definedName name="A83728608R_Data">Data1!$C$11:$C$69</definedName>
+    <definedName name="A83728608R_Latest">Data1!$C$69</definedName>
+    <definedName name="A83728609T">Data1!$L$1:$L$10,Data1!$L$11:$L$69</definedName>
+    <definedName name="A83728609T_Data">Data1!$L$11:$L$69</definedName>
+    <definedName name="A83728609T_Latest">Data1!$L$69</definedName>
+    <definedName name="A83728610A">Data1!$AM$1:$AM$10,Data1!$AM$11:$AM$69</definedName>
+    <definedName name="A83728610A_Data">Data1!$AM$11:$AM$69</definedName>
+    <definedName name="A83728610A_Latest">Data1!$AM$69</definedName>
+    <definedName name="A83728611C">Data1!$U$1:$U$10,Data1!$U$11:$U$69</definedName>
+    <definedName name="A83728611C_Data">Data1!$U$11:$U$69</definedName>
+    <definedName name="A83728611C_Latest">Data1!$U$69</definedName>
+    <definedName name="A83728612F">Data1!$AD$1:$AD$10,Data1!$AD$11:$AD$69</definedName>
+    <definedName name="A83728612F_Data">Data1!$AD$11:$AD$69</definedName>
+    <definedName name="A83728612F_Latest">Data1!$AD$69</definedName>
+    <definedName name="A83728613J">Data1!$D$1:$D$10,Data1!$D$11:$D$69</definedName>
+    <definedName name="A83728613J_Data">Data1!$D$11:$D$69</definedName>
+    <definedName name="A83728613J_Latest">Data1!$D$69</definedName>
+    <definedName name="A83728614K">Data1!$M$1:$M$10,Data1!$M$11:$M$69</definedName>
+    <definedName name="A83728614K_Data">Data1!$M$11:$M$69</definedName>
+    <definedName name="A83728614K_Latest">Data1!$M$69</definedName>
+    <definedName name="A83728615L">Data1!$AN$1:$AN$10,Data1!$AN$11:$AN$69</definedName>
+    <definedName name="A83728615L_Data">Data1!$AN$11:$AN$69</definedName>
+    <definedName name="A83728615L_Latest">Data1!$AN$69</definedName>
+    <definedName name="A83728616R">Data1!$V$1:$V$10,Data1!$V$11:$V$69</definedName>
+    <definedName name="A83728616R_Data">Data1!$V$11:$V$69</definedName>
+    <definedName name="A83728616R_Latest">Data1!$V$69</definedName>
+    <definedName name="A83728617T">Data1!$AE$1:$AE$10,Data1!$AE$11:$AE$69</definedName>
+    <definedName name="A83728617T_Data">Data1!$AE$11:$AE$69</definedName>
+    <definedName name="A83728617T_Latest">Data1!$AE$69</definedName>
+    <definedName name="A83728618V">Data1!$E$1:$E$10,Data1!$E$11:$E$69</definedName>
+    <definedName name="A83728618V_Data">Data1!$E$11:$E$69</definedName>
+    <definedName name="A83728618V_Latest">Data1!$E$69</definedName>
+    <definedName name="A83728619W">Data1!$N$1:$N$10,Data1!$N$11:$N$69</definedName>
+    <definedName name="A83728619W_Data">Data1!$N$11:$N$69</definedName>
+    <definedName name="A83728619W_Latest">Data1!$N$69</definedName>
+    <definedName name="A83728620F">Data1!$AO$1:$AO$10,Data1!$AO$11:$AO$69</definedName>
+    <definedName name="A83728620F_Data">Data1!$AO$11:$AO$69</definedName>
+    <definedName name="A83728620F_Latest">Data1!$AO$69</definedName>
+    <definedName name="A83728621J">Data1!$W$1:$W$10,Data1!$W$11:$W$69</definedName>
+    <definedName name="A83728621J_Data">Data1!$W$11:$W$69</definedName>
+    <definedName name="A83728621J_Latest">Data1!$W$69</definedName>
+    <definedName name="A83728622K">Data1!$AF$1:$AF$10,Data1!$AF$11:$AF$69</definedName>
+    <definedName name="A83728622K_Data">Data1!$AF$11:$AF$69</definedName>
+    <definedName name="A83728622K_Latest">Data1!$AF$69</definedName>
+    <definedName name="A83728623L">Data1!$F$1:$F$10,Data1!$F$11:$F$69</definedName>
+    <definedName name="A83728623L_Data">Data1!$F$11:$F$69</definedName>
+    <definedName name="A83728623L_Latest">Data1!$F$69</definedName>
+    <definedName name="A83728624R">Data1!$O$1:$O$10,Data1!$O$11:$O$69</definedName>
+    <definedName name="A83728624R_Data">Data1!$O$11:$O$69</definedName>
+    <definedName name="A83728624R_Latest">Data1!$O$69</definedName>
+    <definedName name="A83728625T">Data1!$AP$1:$AP$10,Data1!$AP$11:$AP$69</definedName>
+    <definedName name="A83728625T_Data">Data1!$AP$11:$AP$69</definedName>
+    <definedName name="A83728625T_Latest">Data1!$AP$69</definedName>
+    <definedName name="A83728626V">Data1!$X$1:$X$10,Data1!$X$11:$X$69</definedName>
+    <definedName name="A83728626V_Data">Data1!$X$11:$X$69</definedName>
+    <definedName name="A83728626V_Latest">Data1!$X$69</definedName>
+    <definedName name="A83728627W">Data1!$AG$1:$AG$10,Data1!$AG$11:$AG$69</definedName>
+    <definedName name="A83728627W_Data">Data1!$AG$11:$AG$69</definedName>
+    <definedName name="A83728627W_Latest">Data1!$AG$69</definedName>
+    <definedName name="A83728628X">Data1!$G$1:$G$10,Data1!$G$11:$G$69</definedName>
+    <definedName name="A83728628X_Data">Data1!$G$11:$G$69</definedName>
+    <definedName name="A83728628X_Latest">Data1!$G$69</definedName>
+    <definedName name="A83728629A">Data1!$P$1:$P$10,Data1!$P$11:$P$69</definedName>
+    <definedName name="A83728629A_Data">Data1!$P$11:$P$69</definedName>
+    <definedName name="A83728629A_Latest">Data1!$P$69</definedName>
+    <definedName name="A83728630K">Data1!$AQ$1:$AQ$10,Data1!$AQ$11:$AQ$69</definedName>
+    <definedName name="A83728630K_Data">Data1!$AQ$11:$AQ$69</definedName>
+    <definedName name="A83728630K_Latest">Data1!$AQ$69</definedName>
+    <definedName name="A83728631L">Data1!$Y$1:$Y$10,Data1!$Y$11:$Y$69</definedName>
+    <definedName name="A83728631L_Data">Data1!$Y$11:$Y$69</definedName>
+    <definedName name="A83728631L_Latest">Data1!$Y$69</definedName>
+    <definedName name="A83728632R">Data1!$AH$1:$AH$10,Data1!$AH$11:$AH$69</definedName>
+    <definedName name="A83728632R_Data">Data1!$AH$11:$AH$69</definedName>
+    <definedName name="A83728632R_Latest">Data1!$AH$69</definedName>
+    <definedName name="A83728633T">Data1!$H$1:$H$10,Data1!$H$11:$H$69</definedName>
+    <definedName name="A83728633T_Data">Data1!$H$11:$H$69</definedName>
+    <definedName name="A83728633T_Latest">Data1!$H$69</definedName>
+    <definedName name="A83728634V">Data1!$Q$1:$Q$10,Data1!$Q$11:$Q$69</definedName>
+    <definedName name="A83728634V_Data">Data1!$Q$11:$Q$69</definedName>
+    <definedName name="A83728634V_Latest">Data1!$Q$69</definedName>
+    <definedName name="A83728635W">Data1!$AR$1:$AR$10,Data1!$AR$11:$AR$69</definedName>
+    <definedName name="A83728635W_Data">Data1!$AR$11:$AR$69</definedName>
+    <definedName name="A83728635W_Latest">Data1!$AR$69</definedName>
+    <definedName name="A83728636X">Data1!$Z$1:$Z$10,Data1!$Z$11:$Z$69</definedName>
+    <definedName name="A83728636X_Data">Data1!$Z$11:$Z$69</definedName>
+    <definedName name="A83728636X_Latest">Data1!$Z$69</definedName>
+    <definedName name="A83728637A">Data1!$AI$1:$AI$10,Data1!$AI$11:$AI$69</definedName>
+    <definedName name="A83728637A_Data">Data1!$AI$11:$AI$69</definedName>
+    <definedName name="A83728637A_Latest">Data1!$AI$69</definedName>
+    <definedName name="A83728638C">Data1!$I$1:$I$10,Data1!$I$11:$I$69</definedName>
+    <definedName name="A83728638C_Data">Data1!$I$11:$I$69</definedName>
+    <definedName name="A83728638C_Latest">Data1!$I$69</definedName>
+    <definedName name="A83728639F">Data1!$R$1:$R$10,Data1!$R$11:$R$69</definedName>
+    <definedName name="A83728639F_Data">Data1!$R$11:$R$69</definedName>
+    <definedName name="A83728639F_Latest">Data1!$R$69</definedName>
+    <definedName name="A83728640R">Data1!$AS$1:$AS$10,Data1!$AS$11:$AS$69</definedName>
+    <definedName name="A83728640R_Data">Data1!$AS$11:$AS$69</definedName>
+    <definedName name="A83728640R_Latest">Data1!$AS$69</definedName>
+    <definedName name="A83728641T">Data1!$AA$1:$AA$10,Data1!$AA$11:$AA$69</definedName>
+    <definedName name="A83728641T_Data">Data1!$AA$11:$AA$69</definedName>
+    <definedName name="A83728641T_Latest">Data1!$AA$69</definedName>
+    <definedName name="A83728642V">Data1!$AJ$1:$AJ$10,Data1!$AJ$11:$AJ$69</definedName>
+    <definedName name="A83728642V_Data">Data1!$AJ$11:$AJ$69</definedName>
+    <definedName name="A83728642V_Latest">Data1!$AJ$69</definedName>
+    <definedName name="A83728643W">Data1!$J$1:$J$10,Data1!$J$11:$J$69</definedName>
+    <definedName name="A83728643W_Data">Data1!$J$11:$J$69</definedName>
+    <definedName name="A83728643W_Latest">Data1!$J$69</definedName>
+    <definedName name="A83728644X">Data1!$S$1:$S$10,Data1!$S$11:$S$69</definedName>
+    <definedName name="A83728644X_Data">Data1!$S$11:$S$69</definedName>
+    <definedName name="A83728644X_Latest">Data1!$S$69</definedName>
+    <definedName name="A83728645A">Data1!$AT$1:$AT$10,Data1!$AT$11:$AT$69</definedName>
+    <definedName name="A83728645A_Data">Data1!$AT$11:$AT$69</definedName>
+    <definedName name="A83728645A_Latest">Data1!$AT$69</definedName>
+    <definedName name="A83728646C">Data1!$AB$1:$AB$10,Data1!$AB$11:$AB$69</definedName>
+    <definedName name="A83728646C_Data">Data1!$AB$11:$AB$69</definedName>
+    <definedName name="A83728646C_Latest">Data1!$AB$69</definedName>
+    <definedName name="A83728647F">Data1!$AK$1:$AK$10,Data1!$AK$11:$AK$69</definedName>
+    <definedName name="A83728647F_Data">Data1!$AK$11:$AK$69</definedName>
+    <definedName name="A83728647F_Latest">Data1!$AK$69</definedName>
+    <definedName name="Date_Range">Data1!$A$2:$A$10,Data1!$A$11:$A$69</definedName>
+    <definedName name="Date_Range_Data">Data1!$A$11:$A$69</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -165,12 +166,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>ABS</author>
   </authors>
   <commentList>
-    <comment ref="L10" authorId="0" shapeId="0">
+    <comment ref="L10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -189,12 +190,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>ABS</author>
   </authors>
   <commentList>
-    <comment ref="A6" authorId="0" shapeId="0">
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -208,7 +209,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B66" authorId="0" shapeId="0">
+    <comment ref="B67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -221,7 +222,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C66" authorId="0" shapeId="0">
+    <comment ref="C67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -234,7 +235,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D66" authorId="0" shapeId="0">
+    <comment ref="D67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -247,7 +248,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E66" authorId="0" shapeId="0">
+    <comment ref="E67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -260,7 +261,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F66" authorId="0" shapeId="0">
+    <comment ref="F67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -273,7 +274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G66" authorId="0" shapeId="0">
+    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -286,7 +287,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H66" authorId="0" shapeId="0">
+    <comment ref="H67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -299,7 +300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I66" authorId="0" shapeId="0">
+    <comment ref="I67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <r>
           <rPr>
@@ -312,7 +313,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J66" authorId="0" shapeId="0">
+    <comment ref="J67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -325,7 +326,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K66" authorId="0" shapeId="0">
+    <comment ref="K67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -338,7 +339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L66" authorId="0" shapeId="0">
+    <comment ref="L67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -351,7 +352,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M66" authorId="0" shapeId="0">
+    <comment ref="M67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -364,7 +365,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N66" authorId="0" shapeId="0">
+    <comment ref="N67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -377,7 +378,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O66" authorId="0" shapeId="0">
+    <comment ref="O67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -390,7 +391,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P66" authorId="0" shapeId="0">
+    <comment ref="P67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000010000000}">
       <text>
         <r>
           <rPr>
@@ -403,7 +404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q66" authorId="0" shapeId="0">
+    <comment ref="Q67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000011000000}">
       <text>
         <r>
           <rPr>
@@ -416,7 +417,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R66" authorId="0" shapeId="0">
+    <comment ref="R67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000012000000}">
       <text>
         <r>
           <rPr>
@@ -429,7 +430,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S66" authorId="0" shapeId="0">
+    <comment ref="S67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000013000000}">
       <text>
         <r>
           <rPr>
@@ -442,7 +443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T66" authorId="0" shapeId="0">
+    <comment ref="T67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000014000000}">
       <text>
         <r>
           <rPr>
@@ -455,7 +456,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U66" authorId="0" shapeId="0">
+    <comment ref="U67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000015000000}">
       <text>
         <r>
           <rPr>
@@ -468,7 +469,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V66" authorId="0" shapeId="0">
+    <comment ref="V67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000016000000}">
       <text>
         <r>
           <rPr>
@@ -481,7 +482,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W66" authorId="0" shapeId="0">
+    <comment ref="W67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000017000000}">
       <text>
         <r>
           <rPr>
@@ -494,7 +495,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X66" authorId="0" shapeId="0">
+    <comment ref="X67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000018000000}">
       <text>
         <r>
           <rPr>
@@ -507,7 +508,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y66" authorId="0" shapeId="0">
+    <comment ref="Y67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000019000000}">
       <text>
         <r>
           <rPr>
@@ -520,7 +521,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z66" authorId="0" shapeId="0">
+    <comment ref="Z67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001A000000}">
       <text>
         <r>
           <rPr>
@@ -533,7 +534,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA66" authorId="0" shapeId="0">
+    <comment ref="AA67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001B000000}">
       <text>
         <r>
           <rPr>
@@ -546,7 +547,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB66" authorId="0" shapeId="0">
+    <comment ref="AB67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001C000000}">
       <text>
         <r>
           <rPr>
@@ -559,7 +560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC66" authorId="0" shapeId="0">
+    <comment ref="AC67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001D000000}">
       <text>
         <r>
           <rPr>
@@ -572,7 +573,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD66" authorId="0" shapeId="0">
+    <comment ref="AD67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001E000000}">
       <text>
         <r>
           <rPr>
@@ -585,7 +586,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE66" authorId="0" shapeId="0">
+    <comment ref="AE67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00001F000000}">
       <text>
         <r>
           <rPr>
@@ -598,7 +599,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF66" authorId="0" shapeId="0">
+    <comment ref="AF67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000020000000}">
       <text>
         <r>
           <rPr>
@@ -611,7 +612,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG66" authorId="0" shapeId="0">
+    <comment ref="AG67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000021000000}">
       <text>
         <r>
           <rPr>
@@ -624,7 +625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH66" authorId="0" shapeId="0">
+    <comment ref="AH67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000022000000}">
       <text>
         <r>
           <rPr>
@@ -637,7 +638,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ66" authorId="0" shapeId="0">
+    <comment ref="AI67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000023000000}">
       <text>
         <r>
           <rPr>
@@ -650,7 +651,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK66" authorId="0" shapeId="0">
+    <comment ref="AJ67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000024000000}">
       <text>
         <r>
           <rPr>
@@ -663,7 +664,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AL66" authorId="0" shapeId="0">
+    <comment ref="AK67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000025000000}">
       <text>
         <r>
           <rPr>
@@ -676,7 +677,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AM66" authorId="0" shapeId="0">
+    <comment ref="AM67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000026000000}">
       <text>
         <r>
           <rPr>
@@ -689,7 +690,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AN66" authorId="0" shapeId="0">
+    <comment ref="AO67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000027000000}">
       <text>
         <r>
           <rPr>
@@ -702,7 +703,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO66" authorId="0" shapeId="0">
+    <comment ref="AP67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000028000000}">
       <text>
         <r>
           <rPr>
@@ -715,7 +716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AP66" authorId="0" shapeId="0">
+    <comment ref="AT67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000029000000}">
       <text>
         <r>
           <rPr>
@@ -728,7 +729,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AQ66" authorId="0" shapeId="0">
+    <comment ref="B68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00002A000000}">
       <text>
         <r>
           <rPr>
@@ -741,7 +742,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AT66" authorId="0" shapeId="0">
+    <comment ref="C68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00002B000000}">
       <text>
         <r>
           <rPr>
@@ -754,7 +755,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B67" authorId="0" shapeId="0">
+    <comment ref="D68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00002C000000}">
       <text>
         <r>
           <rPr>
@@ -767,7 +768,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C67" authorId="0" shapeId="0">
+    <comment ref="E68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00002D000000}">
       <text>
         <r>
           <rPr>
@@ -780,7 +781,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D67" authorId="0" shapeId="0">
+    <comment ref="F68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00002E000000}">
       <text>
         <r>
           <rPr>
@@ -793,7 +794,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E67" authorId="0" shapeId="0">
+    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00002F000000}">
       <text>
         <r>
           <rPr>
@@ -806,7 +807,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F67" authorId="0" shapeId="0">
+    <comment ref="H68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000030000000}">
       <text>
         <r>
           <rPr>
@@ -819,7 +820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="0" shapeId="0">
+    <comment ref="I68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000031000000}">
       <text>
         <r>
           <rPr>
@@ -832,7 +833,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H67" authorId="0" shapeId="0">
+    <comment ref="J68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000032000000}">
       <text>
         <r>
           <rPr>
@@ -845,7 +846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I67" authorId="0" shapeId="0">
+    <comment ref="K68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000033000000}">
       <text>
         <r>
           <rPr>
@@ -858,7 +859,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J67" authorId="0" shapeId="0">
+    <comment ref="L68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000034000000}">
       <text>
         <r>
           <rPr>
@@ -871,7 +872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K67" authorId="0" shapeId="0">
+    <comment ref="M68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000035000000}">
       <text>
         <r>
           <rPr>
@@ -884,7 +885,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L67" authorId="0" shapeId="0">
+    <comment ref="N68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000036000000}">
       <text>
         <r>
           <rPr>
@@ -897,7 +898,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M67" authorId="0" shapeId="0">
+    <comment ref="O68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000037000000}">
       <text>
         <r>
           <rPr>
@@ -910,7 +911,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N67" authorId="0" shapeId="0">
+    <comment ref="P68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000038000000}">
       <text>
         <r>
           <rPr>
@@ -923,7 +924,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O67" authorId="0" shapeId="0">
+    <comment ref="Q68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000039000000}">
       <text>
         <r>
           <rPr>
@@ -936,7 +937,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P67" authorId="0" shapeId="0">
+    <comment ref="R68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00003A000000}">
       <text>
         <r>
           <rPr>
@@ -949,7 +950,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q67" authorId="0" shapeId="0">
+    <comment ref="S68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00003B000000}">
       <text>
         <r>
           <rPr>
@@ -962,7 +963,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R67" authorId="0" shapeId="0">
+    <comment ref="T68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00003C000000}">
       <text>
         <r>
           <rPr>
@@ -975,7 +976,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S67" authorId="0" shapeId="0">
+    <comment ref="U68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00003D000000}">
       <text>
         <r>
           <rPr>
@@ -988,7 +989,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T67" authorId="0" shapeId="0">
+    <comment ref="V68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00003E000000}">
       <text>
         <r>
           <rPr>
@@ -1001,7 +1002,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U67" authorId="0" shapeId="0">
+    <comment ref="W68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00003F000000}">
       <text>
         <r>
           <rPr>
@@ -1014,7 +1015,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V67" authorId="0" shapeId="0">
+    <comment ref="X68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000040000000}">
       <text>
         <r>
           <rPr>
@@ -1027,7 +1028,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W67" authorId="0" shapeId="0">
+    <comment ref="Y68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000041000000}">
       <text>
         <r>
           <rPr>
@@ -1040,7 +1041,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X67" authorId="0" shapeId="0">
+    <comment ref="Z68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000042000000}">
       <text>
         <r>
           <rPr>
@@ -1053,7 +1054,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y67" authorId="0" shapeId="0">
+    <comment ref="AA68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000043000000}">
       <text>
         <r>
           <rPr>
@@ -1066,7 +1067,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z67" authorId="0" shapeId="0">
+    <comment ref="AB68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000044000000}">
       <text>
         <r>
           <rPr>
@@ -1079,7 +1080,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA67" authorId="0" shapeId="0">
+    <comment ref="AC68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000045000000}">
       <text>
         <r>
           <rPr>
@@ -1092,7 +1093,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB67" authorId="0" shapeId="0">
+    <comment ref="AD68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000046000000}">
       <text>
         <r>
           <rPr>
@@ -1105,7 +1106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC67" authorId="0" shapeId="0">
+    <comment ref="AE68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000047000000}">
       <text>
         <r>
           <rPr>
@@ -1118,7 +1119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD67" authorId="0" shapeId="0">
+    <comment ref="AF68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000048000000}">
       <text>
         <r>
           <rPr>
@@ -1131,7 +1132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE67" authorId="0" shapeId="0">
+    <comment ref="AG68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000049000000}">
       <text>
         <r>
           <rPr>
@@ -1144,7 +1145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF67" authorId="0" shapeId="0">
+    <comment ref="AH68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00004A000000}">
       <text>
         <r>
           <rPr>
@@ -1157,7 +1158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG67" authorId="0" shapeId="0">
+    <comment ref="AI68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00004B000000}">
       <text>
         <r>
           <rPr>
@@ -1170,7 +1171,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH67" authorId="0" shapeId="0">
+    <comment ref="AJ68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00004C000000}">
       <text>
         <r>
           <rPr>
@@ -1183,7 +1184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI67" authorId="0" shapeId="0">
+    <comment ref="AK68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00004D000000}">
       <text>
         <r>
           <rPr>
@@ -1196,7 +1197,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ67" authorId="0" shapeId="0">
+    <comment ref="AL68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00004E000000}">
       <text>
         <r>
           <rPr>
@@ -1209,7 +1210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK67" authorId="0" shapeId="0">
+    <comment ref="AM68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00004F000000}">
       <text>
         <r>
           <rPr>
@@ -1222,7 +1223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AL67" authorId="0" shapeId="0">
+    <comment ref="AN68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000050000000}">
       <text>
         <r>
           <rPr>
@@ -1235,7 +1236,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AM67" authorId="0" shapeId="0">
+    <comment ref="AO68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000051000000}">
       <text>
         <r>
           <rPr>
@@ -1248,7 +1249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AN67" authorId="0" shapeId="0">
+    <comment ref="AQ68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000052000000}">
       <text>
         <r>
           <rPr>
@@ -1261,7 +1262,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO67" authorId="0" shapeId="0">
+    <comment ref="AR68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000053000000}">
       <text>
         <r>
           <rPr>
@@ -1274,7 +1275,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AP67" authorId="0" shapeId="0">
+    <comment ref="AS68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000054000000}">
       <text>
         <r>
           <rPr>
@@ -1287,7 +1288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AQ67" authorId="0" shapeId="0">
+    <comment ref="AT68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000055000000}">
       <text>
         <r>
           <rPr>
@@ -1300,46 +1301,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AR67" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>revised</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AS67" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>revised</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AT67" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>revised</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B68" authorId="0" shapeId="0">
+    <comment ref="B69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000056000000}">
       <text>
         <r>
           <rPr>
@@ -1352,7 +1314,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C68" authorId="0" shapeId="0">
+    <comment ref="C69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000057000000}">
       <text>
         <r>
           <rPr>
@@ -1365,7 +1327,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D68" authorId="0" shapeId="0">
+    <comment ref="D69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000058000000}">
       <text>
         <r>
           <rPr>
@@ -1378,7 +1340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E68" authorId="0" shapeId="0">
+    <comment ref="E69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000059000000}">
       <text>
         <r>
           <rPr>
@@ -1391,7 +1353,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F68" authorId="0" shapeId="0">
+    <comment ref="F69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00005A000000}">
       <text>
         <r>
           <rPr>
@@ -1404,7 +1366,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G68" authorId="0" shapeId="0">
+    <comment ref="G69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00005B000000}">
       <text>
         <r>
           <rPr>
@@ -1417,7 +1379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H68" authorId="0" shapeId="0">
+    <comment ref="H69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00005C000000}">
       <text>
         <r>
           <rPr>
@@ -1430,7 +1392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I68" authorId="0" shapeId="0">
+    <comment ref="I69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00005D000000}">
       <text>
         <r>
           <rPr>
@@ -1443,7 +1405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J68" authorId="0" shapeId="0">
+    <comment ref="J69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00005E000000}">
       <text>
         <r>
           <rPr>
@@ -1456,7 +1418,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K68" authorId="0" shapeId="0">
+    <comment ref="K69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00005F000000}">
       <text>
         <r>
           <rPr>
@@ -1469,7 +1431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L68" authorId="0" shapeId="0">
+    <comment ref="L69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000060000000}">
       <text>
         <r>
           <rPr>
@@ -1482,7 +1444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M68" authorId="0" shapeId="0">
+    <comment ref="M69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000061000000}">
       <text>
         <r>
           <rPr>
@@ -1495,7 +1457,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N68" authorId="0" shapeId="0">
+    <comment ref="N69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000062000000}">
       <text>
         <r>
           <rPr>
@@ -1508,7 +1470,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O68" authorId="0" shapeId="0">
+    <comment ref="O69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000063000000}">
       <text>
         <r>
           <rPr>
@@ -1521,7 +1483,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P68" authorId="0" shapeId="0">
+    <comment ref="P69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000064000000}">
       <text>
         <r>
           <rPr>
@@ -1534,7 +1496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q68" authorId="0" shapeId="0">
+    <comment ref="Q69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000065000000}">
       <text>
         <r>
           <rPr>
@@ -1547,7 +1509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R68" authorId="0" shapeId="0">
+    <comment ref="R69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000066000000}">
       <text>
         <r>
           <rPr>
@@ -1560,7 +1522,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S68" authorId="0" shapeId="0">
+    <comment ref="S69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000067000000}">
       <text>
         <r>
           <rPr>
@@ -1573,7 +1535,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T68" authorId="0" shapeId="0">
+    <comment ref="T69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000068000000}">
       <text>
         <r>
           <rPr>
@@ -1586,7 +1548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U68" authorId="0" shapeId="0">
+    <comment ref="U69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000069000000}">
       <text>
         <r>
           <rPr>
@@ -1599,7 +1561,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V68" authorId="0" shapeId="0">
+    <comment ref="V69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00006A000000}">
       <text>
         <r>
           <rPr>
@@ -1612,7 +1574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W68" authorId="0" shapeId="0">
+    <comment ref="W69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00006B000000}">
       <text>
         <r>
           <rPr>
@@ -1625,7 +1587,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X68" authorId="0" shapeId="0">
+    <comment ref="X69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00006C000000}">
       <text>
         <r>
           <rPr>
@@ -1638,7 +1600,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y68" authorId="0" shapeId="0">
+    <comment ref="Y69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00006D000000}">
       <text>
         <r>
           <rPr>
@@ -1651,7 +1613,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z68" authorId="0" shapeId="0">
+    <comment ref="Z69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00006E000000}">
       <text>
         <r>
           <rPr>
@@ -1664,7 +1626,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA68" authorId="0" shapeId="0">
+    <comment ref="AA69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00006F000000}">
       <text>
         <r>
           <rPr>
@@ -1677,7 +1639,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB68" authorId="0" shapeId="0">
+    <comment ref="AB69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000070000000}">
       <text>
         <r>
           <rPr>
@@ -1690,7 +1652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC68" authorId="0" shapeId="0">
+    <comment ref="AC69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000071000000}">
       <text>
         <r>
           <rPr>
@@ -1703,7 +1665,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD68" authorId="0" shapeId="0">
+    <comment ref="AD69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000072000000}">
       <text>
         <r>
           <rPr>
@@ -1716,7 +1678,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE68" authorId="0" shapeId="0">
+    <comment ref="AE69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000073000000}">
       <text>
         <r>
           <rPr>
@@ -1729,7 +1691,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF68" authorId="0" shapeId="0">
+    <comment ref="AF69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000074000000}">
       <text>
         <r>
           <rPr>
@@ -1742,7 +1704,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG68" authorId="0" shapeId="0">
+    <comment ref="AG69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000075000000}">
       <text>
         <r>
           <rPr>
@@ -1755,7 +1717,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH68" authorId="0" shapeId="0">
+    <comment ref="AH69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000076000000}">
       <text>
         <r>
           <rPr>
@@ -1768,7 +1730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI68" authorId="0" shapeId="0">
+    <comment ref="AI69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000077000000}">
       <text>
         <r>
           <rPr>
@@ -1781,7 +1743,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ68" authorId="0" shapeId="0">
+    <comment ref="AJ69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000078000000}">
       <text>
         <r>
           <rPr>
@@ -1794,7 +1756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK68" authorId="0" shapeId="0">
+    <comment ref="AK69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000079000000}">
       <text>
         <r>
           <rPr>
@@ -1807,7 +1769,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AL68" authorId="0" shapeId="0">
+    <comment ref="AL69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00007A000000}">
       <text>
         <r>
           <rPr>
@@ -1820,7 +1782,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AM68" authorId="0" shapeId="0">
+    <comment ref="AM69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00007B000000}">
       <text>
         <r>
           <rPr>
@@ -1833,7 +1795,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AN68" authorId="0" shapeId="0">
+    <comment ref="AN69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00007C000000}">
       <text>
         <r>
           <rPr>
@@ -1846,7 +1808,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AO68" authorId="0" shapeId="0">
+    <comment ref="AO69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00007D000000}">
       <text>
         <r>
           <rPr>
@@ -1859,7 +1821,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AP68" authorId="0" shapeId="0">
+    <comment ref="AP69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00007E000000}">
       <text>
         <r>
           <rPr>
@@ -1872,7 +1834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AQ68" authorId="0" shapeId="0">
+    <comment ref="AQ69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00007F000000}">
       <text>
         <r>
           <rPr>
@@ -1885,7 +1847,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AR68" authorId="0" shapeId="0">
+    <comment ref="AR69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000080000000}">
       <text>
         <r>
           <rPr>
@@ -1898,7 +1860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AS68" authorId="0" shapeId="0">
+    <comment ref="AS69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000081000000}">
       <text>
         <r>
           <rPr>
@@ -1911,7 +1873,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AT68" authorId="0" shapeId="0">
+    <comment ref="AT69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000082000000}">
       <text>
         <r>
           <rPr>
@@ -2282,7 +2244,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mmm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0;\-0.0;0.0;@"/>
@@ -2398,23 +2360,23 @@
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2429,9 +2391,6 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2450,6 +2409,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2486,7 +2448,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2535,7 +2503,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks/>
         </xdr:cNvPicPr>
@@ -2829,7 +2803,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:M58"/>
   <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2895,57 +2869,57 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
     </row>
     <row r="8" spans="1:13" ht="15" x14ac:dyDescent="0.25">
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="18" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19" t="s">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="18" t="s">
         <v>49</v>
       </c>
     </row>
@@ -2956,17 +2930,17 @@
       <c r="D12" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="19" t="s">
         <v>58</v>
       </c>
       <c r="F12" s="10">
         <v>40787</v>
       </c>
       <c r="G12" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H12" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>54</v>
@@ -2988,17 +2962,17 @@
       <c r="D13" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="19" t="s">
         <v>59</v>
       </c>
       <c r="F13" s="10">
         <v>40787</v>
       </c>
       <c r="G13" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H13" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>54</v>
@@ -3020,17 +2994,17 @@
       <c r="D14" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="19" t="s">
         <v>60</v>
       </c>
       <c r="F14" s="10">
         <v>40787</v>
       </c>
       <c r="G14" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H14" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>54</v>
@@ -3052,17 +3026,17 @@
       <c r="D15" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="19" t="s">
         <v>61</v>
       </c>
       <c r="F15" s="10">
         <v>40787</v>
       </c>
       <c r="G15" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H15" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I15" s="11" t="s">
         <v>54</v>
@@ -3084,17 +3058,17 @@
       <c r="D16" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="19" t="s">
         <v>62</v>
       </c>
       <c r="F16" s="10">
         <v>40787</v>
       </c>
       <c r="G16" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H16" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>54</v>
@@ -3116,17 +3090,17 @@
       <c r="D17" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="19" t="s">
         <v>63</v>
       </c>
       <c r="F17" s="10">
         <v>40787</v>
       </c>
       <c r="G17" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H17" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>54</v>
@@ -3148,17 +3122,17 @@
       <c r="D18" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="19" t="s">
         <v>64</v>
       </c>
       <c r="F18" s="10">
         <v>40787</v>
       </c>
       <c r="G18" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H18" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I18" s="11" t="s">
         <v>54</v>
@@ -3180,17 +3154,17 @@
       <c r="D19" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="19" t="s">
         <v>65</v>
       </c>
       <c r="F19" s="10">
         <v>40787</v>
       </c>
       <c r="G19" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H19" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I19" s="11" t="s">
         <v>54</v>
@@ -3212,17 +3186,17 @@
       <c r="D20" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="19" t="s">
         <v>66</v>
       </c>
       <c r="F20" s="10">
         <v>40787</v>
       </c>
       <c r="G20" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H20" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I20" s="11" t="s">
         <v>54</v>
@@ -3244,17 +3218,17 @@
       <c r="D21" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="19" t="s">
         <v>67</v>
       </c>
       <c r="F21" s="10">
         <v>40787</v>
       </c>
       <c r="G21" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H21" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I21" s="11" t="s">
         <v>54</v>
@@ -3276,17 +3250,17 @@
       <c r="D22" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="19" t="s">
         <v>68</v>
       </c>
       <c r="F22" s="10">
         <v>40787</v>
       </c>
       <c r="G22" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H22" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I22" s="11" t="s">
         <v>54</v>
@@ -3308,17 +3282,17 @@
       <c r="D23" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="19" t="s">
         <v>69</v>
       </c>
       <c r="F23" s="10">
         <v>40787</v>
       </c>
       <c r="G23" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H23" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I23" s="11" t="s">
         <v>54</v>
@@ -3340,17 +3314,17 @@
       <c r="D24" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="19" t="s">
         <v>70</v>
       </c>
       <c r="F24" s="10">
         <v>40787</v>
       </c>
       <c r="G24" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H24" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I24" s="11" t="s">
         <v>54</v>
@@ -3372,17 +3346,17 @@
       <c r="D25" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="19" t="s">
         <v>71</v>
       </c>
       <c r="F25" s="10">
         <v>40787</v>
       </c>
       <c r="G25" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H25" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I25" s="11" t="s">
         <v>54</v>
@@ -3404,17 +3378,17 @@
       <c r="D26" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="19" t="s">
         <v>72</v>
       </c>
       <c r="F26" s="10">
         <v>40787</v>
       </c>
       <c r="G26" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H26" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I26" s="11" t="s">
         <v>54</v>
@@ -3436,17 +3410,17 @@
       <c r="D27" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="19" t="s">
         <v>73</v>
       </c>
       <c r="F27" s="10">
         <v>40787</v>
       </c>
       <c r="G27" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H27" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I27" s="11" t="s">
         <v>54</v>
@@ -3468,17 +3442,17 @@
       <c r="D28" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="19" t="s">
         <v>74</v>
       </c>
       <c r="F28" s="10">
         <v>40787</v>
       </c>
       <c r="G28" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H28" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I28" s="11" t="s">
         <v>54</v>
@@ -3500,17 +3474,17 @@
       <c r="D29" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="19" t="s">
         <v>75</v>
       </c>
       <c r="F29" s="10">
         <v>40787</v>
       </c>
       <c r="G29" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H29" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I29" s="11" t="s">
         <v>54</v>
@@ -3532,17 +3506,17 @@
       <c r="D30" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F30" s="10">
         <v>40787</v>
       </c>
       <c r="G30" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H30" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I30" s="11" t="s">
         <v>54</v>
@@ -3564,17 +3538,17 @@
       <c r="D31" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="E31" s="19" t="s">
         <v>77</v>
       </c>
       <c r="F31" s="10">
         <v>40787</v>
       </c>
       <c r="G31" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H31" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I31" s="11" t="s">
         <v>54</v>
@@ -3596,17 +3570,17 @@
       <c r="D32" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="19" t="s">
         <v>78</v>
       </c>
       <c r="F32" s="10">
         <v>40787</v>
       </c>
       <c r="G32" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H32" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I32" s="11" t="s">
         <v>54</v>
@@ -3628,17 +3602,17 @@
       <c r="D33" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="19" t="s">
         <v>79</v>
       </c>
       <c r="F33" s="10">
         <v>40787</v>
       </c>
       <c r="G33" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H33" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I33" s="11" t="s">
         <v>54</v>
@@ -3660,17 +3634,17 @@
       <c r="D34" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="19" t="s">
         <v>80</v>
       </c>
       <c r="F34" s="10">
         <v>40787</v>
       </c>
       <c r="G34" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H34" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I34" s="11" t="s">
         <v>54</v>
@@ -3692,17 +3666,17 @@
       <c r="D35" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="E35" s="19" t="s">
         <v>81</v>
       </c>
       <c r="F35" s="10">
         <v>40787</v>
       </c>
       <c r="G35" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H35" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I35" s="11" t="s">
         <v>54</v>
@@ -3724,17 +3698,17 @@
       <c r="D36" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="19" t="s">
         <v>82</v>
       </c>
       <c r="F36" s="10">
         <v>40787</v>
       </c>
       <c r="G36" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H36" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I36" s="11" t="s">
         <v>54</v>
@@ -3756,17 +3730,17 @@
       <c r="D37" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F37" s="10">
         <v>40787</v>
       </c>
       <c r="G37" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H37" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I37" s="11" t="s">
         <v>54</v>
@@ -3788,17 +3762,17 @@
       <c r="D38" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="19" t="s">
         <v>84</v>
       </c>
       <c r="F38" s="10">
         <v>40787</v>
       </c>
       <c r="G38" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H38" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I38" s="11" t="s">
         <v>54</v>
@@ -3820,17 +3794,17 @@
       <c r="D39" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="19" t="s">
         <v>87</v>
       </c>
       <c r="F39" s="10">
         <v>40787</v>
       </c>
       <c r="G39" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H39" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I39" s="11" t="s">
         <v>85</v>
@@ -3852,17 +3826,17 @@
       <c r="D40" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="19" t="s">
         <v>88</v>
       </c>
       <c r="F40" s="10">
         <v>40787</v>
       </c>
       <c r="G40" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H40" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I40" s="11" t="s">
         <v>85</v>
@@ -3884,17 +3858,17 @@
       <c r="D41" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="19" t="s">
         <v>89</v>
       </c>
       <c r="F41" s="10">
         <v>40787</v>
       </c>
       <c r="G41" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H41" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I41" s="11" t="s">
         <v>85</v>
@@ -3916,17 +3890,17 @@
       <c r="D42" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="19" t="s">
         <v>90</v>
       </c>
       <c r="F42" s="10">
         <v>40787</v>
       </c>
       <c r="G42" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H42" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I42" s="11" t="s">
         <v>85</v>
@@ -3948,17 +3922,17 @@
       <c r="D43" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="19" t="s">
         <v>91</v>
       </c>
       <c r="F43" s="10">
         <v>40787</v>
       </c>
       <c r="G43" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H43" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I43" s="11" t="s">
         <v>85</v>
@@ -3980,17 +3954,17 @@
       <c r="D44" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E44" s="20" t="s">
+      <c r="E44" s="19" t="s">
         <v>92</v>
       </c>
       <c r="F44" s="10">
         <v>40787</v>
       </c>
       <c r="G44" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H44" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I44" s="11" t="s">
         <v>85</v>
@@ -4012,17 +3986,17 @@
       <c r="D45" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="19" t="s">
         <v>93</v>
       </c>
       <c r="F45" s="10">
         <v>40787</v>
       </c>
       <c r="G45" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H45" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I45" s="11" t="s">
         <v>85</v>
@@ -4044,17 +4018,17 @@
       <c r="D46" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="19" t="s">
         <v>94</v>
       </c>
       <c r="F46" s="10">
         <v>40787</v>
       </c>
       <c r="G46" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H46" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I46" s="11" t="s">
         <v>85</v>
@@ -4076,17 +4050,17 @@
       <c r="D47" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E47" s="19" t="s">
         <v>95</v>
       </c>
       <c r="F47" s="10">
         <v>40787</v>
       </c>
       <c r="G47" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H47" s="11">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I47" s="11" t="s">
         <v>85</v>
@@ -4108,19 +4082,19 @@
       <c r="D48" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="E48" s="19" t="s">
         <v>97</v>
       </c>
       <c r="F48" s="10">
         <v>40787</v>
       </c>
       <c r="G48" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H48" s="11">
-        <v>58</v>
-      </c>
-      <c r="I48" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="I48" s="20" t="s">
         <v>96</v>
       </c>
       <c r="J48" s="11" t="s">
@@ -4140,19 +4114,19 @@
       <c r="D49" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="19" t="s">
         <v>98</v>
       </c>
       <c r="F49" s="10">
         <v>40787</v>
       </c>
       <c r="G49" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H49" s="11">
-        <v>58</v>
-      </c>
-      <c r="I49" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="I49" s="20" t="s">
         <v>96</v>
       </c>
       <c r="J49" s="11" t="s">
@@ -4172,19 +4146,19 @@
       <c r="D50" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="E50" s="19" t="s">
         <v>99</v>
       </c>
       <c r="F50" s="10">
         <v>40787</v>
       </c>
       <c r="G50" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H50" s="11">
-        <v>58</v>
-      </c>
-      <c r="I50" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="I50" s="20" t="s">
         <v>96</v>
       </c>
       <c r="J50" s="11" t="s">
@@ -4204,19 +4178,19 @@
       <c r="D51" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E51" s="20" t="s">
+      <c r="E51" s="19" t="s">
         <v>100</v>
       </c>
       <c r="F51" s="10">
         <v>40787</v>
       </c>
       <c r="G51" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H51" s="11">
-        <v>58</v>
-      </c>
-      <c r="I51" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="I51" s="20" t="s">
         <v>96</v>
       </c>
       <c r="J51" s="11" t="s">
@@ -4236,19 +4210,19 @@
       <c r="D52" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E52" s="20" t="s">
+      <c r="E52" s="19" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="10">
         <v>40787</v>
       </c>
       <c r="G52" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H52" s="11">
-        <v>58</v>
-      </c>
-      <c r="I52" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="I52" s="20" t="s">
         <v>96</v>
       </c>
       <c r="J52" s="11" t="s">
@@ -4268,19 +4242,19 @@
       <c r="D53" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="19" t="s">
         <v>102</v>
       </c>
       <c r="F53" s="10">
         <v>40787</v>
       </c>
       <c r="G53" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H53" s="11">
-        <v>58</v>
-      </c>
-      <c r="I53" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="I53" s="20" t="s">
         <v>96</v>
       </c>
       <c r="J53" s="11" t="s">
@@ -4300,19 +4274,19 @@
       <c r="D54" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="19" t="s">
         <v>103</v>
       </c>
       <c r="F54" s="10">
         <v>40787</v>
       </c>
       <c r="G54" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H54" s="11">
-        <v>58</v>
-      </c>
-      <c r="I54" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="I54" s="20" t="s">
         <v>96</v>
       </c>
       <c r="J54" s="11" t="s">
@@ -4332,19 +4306,19 @@
       <c r="D55" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="19" t="s">
         <v>104</v>
       </c>
       <c r="F55" s="10">
         <v>40787</v>
       </c>
       <c r="G55" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H55" s="11">
-        <v>58</v>
-      </c>
-      <c r="I55" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="I55" s="20" t="s">
         <v>96</v>
       </c>
       <c r="J55" s="11" t="s">
@@ -4364,19 +4338,19 @@
       <c r="D56" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E56" s="20" t="s">
+      <c r="E56" s="19" t="s">
         <v>105</v>
       </c>
       <c r="F56" s="10">
         <v>40787</v>
       </c>
       <c r="G56" s="10">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H56" s="11">
-        <v>58</v>
-      </c>
-      <c r="I56" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="I56" s="20" t="s">
         <v>96</v>
       </c>
       <c r="J56" s="11" t="s">
@@ -4399,52 +4373,52 @@
     <mergeCell ref="B6:L6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D8" location="Enquiries!A1" display="Enquiries"/>
-    <hyperlink ref="E12" location="A83728603C" display="A83728603C"/>
-    <hyperlink ref="E13" location="A83728608R" display="A83728608R"/>
-    <hyperlink ref="E14" location="A83728613J" display="A83728613J"/>
-    <hyperlink ref="E15" location="A83728618V" display="A83728618V"/>
-    <hyperlink ref="E16" location="A83728623L" display="A83728623L"/>
-    <hyperlink ref="E17" location="A83728628X" display="A83728628X"/>
-    <hyperlink ref="E18" location="A83728633T" display="A83728633T"/>
-    <hyperlink ref="E19" location="A83728638C" display="A83728638C"/>
-    <hyperlink ref="E20" location="A83728643W" display="A83728643W"/>
-    <hyperlink ref="E21" location="A83728604F" display="A83728604F"/>
-    <hyperlink ref="E22" location="A83728609T" display="A83728609T"/>
-    <hyperlink ref="E23" location="A83728614K" display="A83728614K"/>
-    <hyperlink ref="E24" location="A83728619W" display="A83728619W"/>
-    <hyperlink ref="E25" location="A83728624R" display="A83728624R"/>
-    <hyperlink ref="E26" location="A83728629A" display="A83728629A"/>
-    <hyperlink ref="E27" location="A83728634V" display="A83728634V"/>
-    <hyperlink ref="E28" location="A83728639F" display="A83728639F"/>
-    <hyperlink ref="E29" location="A83728644X" display="A83728644X"/>
-    <hyperlink ref="E30" location="A83728606K" display="A83728606K"/>
-    <hyperlink ref="E31" location="A83728611C" display="A83728611C"/>
-    <hyperlink ref="E32" location="A83728616R" display="A83728616R"/>
-    <hyperlink ref="E33" location="A83728621J" display="A83728621J"/>
-    <hyperlink ref="E34" location="A83728626V" display="A83728626V"/>
-    <hyperlink ref="E35" location="A83728631L" display="A83728631L"/>
-    <hyperlink ref="E36" location="A83728636X" display="A83728636X"/>
-    <hyperlink ref="E37" location="A83728641T" display="A83728641T"/>
-    <hyperlink ref="E38" location="A83728646C" display="A83728646C"/>
-    <hyperlink ref="E39" location="A83728607L" display="A83728607L"/>
-    <hyperlink ref="E40" location="A83728612F" display="A83728612F"/>
-    <hyperlink ref="E41" location="A83728617T" display="A83728617T"/>
-    <hyperlink ref="E42" location="A83728622K" display="A83728622K"/>
-    <hyperlink ref="E43" location="A83728627W" display="A83728627W"/>
-    <hyperlink ref="E44" location="A83728632R" display="A83728632R"/>
-    <hyperlink ref="E45" location="A83728637A" display="A83728637A"/>
-    <hyperlink ref="E46" location="A83728642V" display="A83728642V"/>
-    <hyperlink ref="E47" location="A83728647F" display="A83728647F"/>
-    <hyperlink ref="E48" location="A83728605J" display="A83728605J"/>
-    <hyperlink ref="E49" location="A83728610A" display="A83728610A"/>
-    <hyperlink ref="E50" location="A83728615L" display="A83728615L"/>
-    <hyperlink ref="E51" location="A83728620F" display="A83728620F"/>
-    <hyperlink ref="E52" location="A83728625T" display="A83728625T"/>
-    <hyperlink ref="E53" location="A83728630K" display="A83728630K"/>
-    <hyperlink ref="E54" location="A83728635W" display="A83728635W"/>
-    <hyperlink ref="E55" location="A83728640R" display="A83728640R"/>
-    <hyperlink ref="E56" location="A83728645A" display="A83728645A"/>
+    <hyperlink ref="D8" location="Enquiries!A1" display="Enquiries" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E12" location="A83728603C" display="A83728603C" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E13" location="A83728608R" display="A83728608R" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E14" location="A83728613J" display="A83728613J" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="E15" location="A83728618V" display="A83728618V" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="E16" location="A83728623L" display="A83728623L" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="E17" location="A83728628X" display="A83728628X" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="E18" location="A83728633T" display="A83728633T" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="E19" location="A83728638C" display="A83728638C" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="E20" location="A83728643W" display="A83728643W" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="E21" location="A83728604F" display="A83728604F" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="E22" location="A83728609T" display="A83728609T" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="E23" location="A83728614K" display="A83728614K" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="E24" location="A83728619W" display="A83728619W" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="E25" location="A83728624R" display="A83728624R" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="E26" location="A83728629A" display="A83728629A" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="E27" location="A83728634V" display="A83728634V" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="E28" location="A83728639F" display="A83728639F" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="E29" location="A83728644X" display="A83728644X" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="E30" location="A83728606K" display="A83728606K" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="E31" location="A83728611C" display="A83728611C" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="E32" location="A83728616R" display="A83728616R" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="E33" location="A83728621J" display="A83728621J" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="E34" location="A83728626V" display="A83728626V" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="E35" location="A83728631L" display="A83728631L" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="E36" location="A83728636X" display="A83728636X" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="E37" location="A83728641T" display="A83728641T" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="E38" location="A83728646C" display="A83728646C" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="E39" location="A83728607L" display="A83728607L" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="E40" location="A83728612F" display="A83728612F" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="E41" location="A83728617T" display="A83728617T" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="E42" location="A83728622K" display="A83728622K" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="E43" location="A83728627W" display="A83728627W" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="E44" location="A83728632R" display="A83728632R" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="E45" location="A83728637A" display="A83728637A" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="E46" location="A83728642V" display="A83728642V" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="E47" location="A83728647F" display="A83728647F" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="E48" location="A83728605J" display="A83728605J" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="E49" location="A83728610A" display="A83728610A" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="E50" location="A83728615L" display="A83728615L" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="E51" location="A83728620F" display="A83728620F" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="E52" location="A83728625T" display="A83728625T" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="E53" location="A83728630K" display="A83728630K" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="E54" location="A83728635W" display="A83728635W" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="E55" location="A83728640R" display="A83728640R" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="E56" location="A83728645A" display="A83728645A" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4453,8 +4427,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AT68"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:AT69"/>
   <sheetFormatPr defaultColWidth="14.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="14.7109375" style="1"/>
@@ -5442,139 +5416,139 @@
         <v>51</v>
       </c>
       <c r="B8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="C8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="D8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="E8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="F8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="G8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="H8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="I8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="J8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="K8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="L8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="M8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="N8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="O8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="P8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="Q8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="R8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="S8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="T8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="U8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="V8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="W8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="X8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="Y8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="Z8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AA8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AB8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AC8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AD8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AE8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AF8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AG8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AH8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AI8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AJ8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AK8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AL8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AM8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AN8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AO8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AP8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AQ8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AR8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AS8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="AT8" s="6">
-        <v>45992</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="9" spans="1:46" x14ac:dyDescent="0.2">
@@ -5582,139 +5556,139 @@
         <v>52</v>
       </c>
       <c r="B9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Y9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AB9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AC9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AD9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AE9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AF9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AG9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AH9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AI9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AK9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AL9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AM9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AN9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AO9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AP9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AQ9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AR9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AS9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AT9" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:46" x14ac:dyDescent="0.2">
@@ -13702,127 +13676,127 @@
         <v>45901</v>
       </c>
       <c r="B67" s="9">
-        <v>4334762.8</v>
+        <v>4369237.5999999996</v>
       </c>
       <c r="C67" s="9">
-        <v>2698633.4</v>
+        <v>2707566.9</v>
       </c>
       <c r="D67" s="9">
-        <v>2236035.6</v>
+        <v>2243731.7999999998</v>
       </c>
       <c r="E67" s="9">
-        <v>713422.5</v>
+        <v>713350.5</v>
       </c>
       <c r="F67" s="9">
-        <v>1075000.3999999999</v>
+        <v>1076011</v>
       </c>
       <c r="G67" s="9">
-        <v>172767.8</v>
+        <v>175052.2</v>
       </c>
       <c r="H67" s="9">
-        <v>40992.400000000001</v>
+        <v>40989.300000000003</v>
       </c>
       <c r="I67" s="9">
-        <v>181134.6</v>
+        <v>180246.2</v>
       </c>
       <c r="J67" s="9">
-        <v>11452749.4</v>
+        <v>11506185.4</v>
       </c>
       <c r="K67" s="9">
-        <v>179992</v>
+        <v>181431.9</v>
       </c>
       <c r="L67" s="9">
-        <v>74626.899999999994</v>
+        <v>74898.600000000006</v>
       </c>
       <c r="M67" s="9">
-        <v>94946.4</v>
+        <v>95244.5</v>
       </c>
       <c r="N67" s="9">
-        <v>39126</v>
+        <v>39113.5</v>
       </c>
       <c r="O67" s="9">
-        <v>49101.9</v>
+        <v>49120.6</v>
       </c>
       <c r="P67" s="9">
-        <v>9790.2999999999993</v>
+        <v>9977.2000000000007</v>
       </c>
       <c r="Q67" s="9">
-        <v>9193.6</v>
+        <v>9191.2000000000007</v>
       </c>
       <c r="R67" s="9">
-        <v>12828.3</v>
+        <v>12774.7</v>
       </c>
       <c r="S67" s="9">
-        <v>469605.4</v>
+        <v>471752</v>
       </c>
       <c r="T67" s="9">
-        <v>4514754.8</v>
+        <v>4550669.4000000004</v>
       </c>
       <c r="U67" s="9">
-        <v>2773260.2</v>
+        <v>2782465.5</v>
       </c>
       <c r="V67" s="9">
-        <v>2330982</v>
+        <v>2338976.2999999998</v>
       </c>
       <c r="W67" s="9">
-        <v>752548.5</v>
+        <v>752463.9</v>
       </c>
       <c r="X67" s="9">
-        <v>1124102.3</v>
+        <v>1125131.5</v>
       </c>
       <c r="Y67" s="9">
-        <v>182558</v>
+        <v>185029.3</v>
       </c>
       <c r="Z67" s="9">
-        <v>50186</v>
+        <v>50180.5</v>
       </c>
       <c r="AA67" s="9">
-        <v>193962.9</v>
+        <v>193020.9</v>
       </c>
       <c r="AB67" s="9">
-        <v>11922354.699999999</v>
+        <v>11977937.5</v>
       </c>
       <c r="AC67" s="9">
-        <v>1285.2</v>
+        <v>1295.5</v>
       </c>
       <c r="AD67" s="9">
-        <v>923.9</v>
+        <v>926.9</v>
       </c>
       <c r="AE67" s="9">
-        <v>1017.2</v>
+        <v>1020.7</v>
       </c>
       <c r="AF67" s="9">
-        <v>897.3</v>
+        <v>897.1</v>
       </c>
       <c r="AG67" s="9">
-        <v>943.7</v>
+        <v>944.5</v>
       </c>
       <c r="AH67" s="9">
-        <v>680.5</v>
+        <v>689.7</v>
       </c>
       <c r="AI67" s="9">
-        <v>555.6</v>
+        <v>555.5</v>
       </c>
       <c r="AJ67" s="9">
-        <v>953.5</v>
+        <v>948.9</v>
       </c>
       <c r="AK67" s="9">
-        <v>1046</v>
+        <v>1050.9000000000001</v>
       </c>
       <c r="AL67" s="9">
         <v>3512.8</v>
       </c>
       <c r="AM67" s="9">
-        <v>3001.8</v>
+        <v>3002</v>
       </c>
       <c r="AN67" s="9">
         <v>2291.5</v>
       </c>
       <c r="AO67" s="9">
-        <v>838.7</v>
+        <v>838.8</v>
       </c>
       <c r="AP67" s="9">
-        <v>1191.2</v>
+        <v>1191.3</v>
       </c>
       <c r="AQ67" s="9">
         <v>268.3</v>
@@ -13834,7 +13808,7 @@
         <v>203.4</v>
       </c>
       <c r="AT67" s="9">
-        <v>11398.1</v>
+        <v>11398.3</v>
       </c>
     </row>
     <row r="68" spans="1:46" x14ac:dyDescent="0.2">
@@ -13842,139 +13816,279 @@
         <v>45992</v>
       </c>
       <c r="B68" s="9">
-        <v>4409777.9000000004</v>
+        <v>4464985.9000000004</v>
       </c>
       <c r="C68" s="9">
-        <v>2740546.4</v>
+        <v>2785566</v>
       </c>
       <c r="D68" s="9">
-        <v>2355283.7000000002</v>
+        <v>2369481.2999999998</v>
       </c>
       <c r="E68" s="9">
-        <v>747898.3</v>
+        <v>749043.3</v>
       </c>
       <c r="F68" s="9">
-        <v>1159353.8999999999</v>
+        <v>1176889.3</v>
       </c>
       <c r="G68" s="9">
-        <v>179282.2</v>
+        <v>183833.4</v>
       </c>
       <c r="H68" s="9">
-        <v>42929.5</v>
+        <v>43143.5</v>
       </c>
       <c r="I68" s="9">
-        <v>186254.4</v>
+        <v>191806.4</v>
       </c>
       <c r="J68" s="9">
-        <v>11821326.4</v>
+        <v>11964749.1</v>
       </c>
       <c r="K68" s="9">
-        <v>183106.9</v>
+        <v>185954.7</v>
       </c>
       <c r="L68" s="9">
-        <v>75785.899999999994</v>
+        <v>77279.8</v>
       </c>
       <c r="M68" s="9">
-        <v>100010</v>
+        <v>100586</v>
       </c>
       <c r="N68" s="9">
-        <v>41016.699999999997</v>
+        <v>41148.9</v>
       </c>
       <c r="O68" s="9">
-        <v>52954.9</v>
+        <v>53987.5</v>
       </c>
       <c r="P68" s="9">
-        <v>10159.4</v>
+        <v>10319.1</v>
       </c>
       <c r="Q68" s="9">
-        <v>9628</v>
+        <v>9221.2999999999993</v>
       </c>
       <c r="R68" s="9">
-        <v>13190.9</v>
+        <v>13515.3</v>
       </c>
       <c r="S68" s="9">
-        <v>485852.7</v>
+        <v>492012.7</v>
       </c>
       <c r="T68" s="9">
-        <v>4592884.8</v>
+        <v>4650940.5</v>
       </c>
       <c r="U68" s="9">
-        <v>2816332.3</v>
+        <v>2862845.8</v>
       </c>
       <c r="V68" s="9">
-        <v>2455293.7000000002</v>
+        <v>2470067.2999999998</v>
       </c>
       <c r="W68" s="9">
-        <v>788915</v>
+        <v>790192.2</v>
       </c>
       <c r="X68" s="9">
-        <v>1212308.8</v>
+        <v>1230876.8999999999</v>
       </c>
       <c r="Y68" s="9">
-        <v>189441.7</v>
+        <v>194152.6</v>
       </c>
       <c r="Z68" s="9">
-        <v>52557.5</v>
+        <v>52364.7</v>
       </c>
       <c r="AA68" s="9">
-        <v>199445.4</v>
+        <v>205321.8</v>
       </c>
       <c r="AB68" s="9">
-        <v>12307179</v>
+        <v>12456761.800000001</v>
       </c>
       <c r="AC68" s="9">
-        <v>1301.0999999999999</v>
+        <v>1319.5</v>
       </c>
       <c r="AD68" s="9">
-        <v>933.1</v>
+        <v>949.5</v>
       </c>
       <c r="AE68" s="9">
-        <v>1066</v>
+        <v>1073.9000000000001</v>
       </c>
       <c r="AF68" s="9">
-        <v>938.1</v>
+        <v>938.7</v>
       </c>
       <c r="AG68" s="9">
-        <v>1014.2</v>
+        <v>1029.8</v>
       </c>
       <c r="AH68" s="9">
-        <v>703.8</v>
+        <v>722.1</v>
       </c>
       <c r="AI68" s="9">
-        <v>580</v>
+        <v>578.79999999999995</v>
       </c>
       <c r="AJ68" s="9">
-        <v>973.8</v>
+        <v>1004.3</v>
       </c>
       <c r="AK68" s="9">
-        <v>1074.7</v>
+        <v>1088.8</v>
       </c>
       <c r="AL68" s="9">
-        <v>3529.9</v>
+        <v>3524.9</v>
       </c>
       <c r="AM68" s="9">
-        <v>3018.1</v>
+        <v>3015.1</v>
       </c>
       <c r="AN68" s="9">
-        <v>2303.3000000000002</v>
+        <v>2300</v>
       </c>
       <c r="AO68" s="9">
-        <v>841</v>
+        <v>841.8</v>
       </c>
       <c r="AP68" s="9">
         <v>1195.3</v>
       </c>
       <c r="AQ68" s="9">
-        <v>269.2</v>
+        <v>268.89999999999998</v>
       </c>
       <c r="AR68" s="9">
-        <v>90.6</v>
+        <v>90.5</v>
       </c>
       <c r="AS68" s="9">
-        <v>204.8</v>
+        <v>204.4</v>
       </c>
       <c r="AT68" s="9">
-        <v>11452.2</v>
+        <v>11441</v>
+      </c>
+    </row>
+    <row r="69" spans="1:46" x14ac:dyDescent="0.2">
+      <c r="A69" s="10">
+        <v>46082</v>
+      </c>
+      <c r="B69" s="9">
+        <v>4504778.3</v>
+      </c>
+      <c r="C69" s="9">
+        <v>2793631.3</v>
+      </c>
+      <c r="D69" s="9">
+        <v>2492175.7000000002</v>
+      </c>
+      <c r="E69" s="9">
+        <v>778612.8</v>
+      </c>
+      <c r="F69" s="9">
+        <v>1265542.5</v>
+      </c>
+      <c r="G69" s="9">
+        <v>191636.6</v>
+      </c>
+      <c r="H69" s="9">
+        <v>44662.400000000001</v>
+      </c>
+      <c r="I69" s="9">
+        <v>195744.7</v>
+      </c>
+      <c r="J69" s="9">
+        <v>12266784.199999999</v>
+      </c>
+      <c r="K69" s="9">
+        <v>187611.9</v>
+      </c>
+      <c r="L69" s="9">
+        <v>77503.5</v>
+      </c>
+      <c r="M69" s="9">
+        <v>105794.5</v>
+      </c>
+      <c r="N69" s="9">
+        <v>42773.4</v>
+      </c>
+      <c r="O69" s="9">
+        <v>58054.3</v>
+      </c>
+      <c r="P69" s="9">
+        <v>10757.1</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>9545.9</v>
+      </c>
+      <c r="R69" s="9">
+        <v>13792.8</v>
+      </c>
+      <c r="S69" s="9">
+        <v>505833.5</v>
+      </c>
+      <c r="T69" s="9">
+        <v>4692390.2</v>
+      </c>
+      <c r="U69" s="9">
+        <v>2871134.8</v>
+      </c>
+      <c r="V69" s="9">
+        <v>2597970.2000000002</v>
+      </c>
+      <c r="W69" s="9">
+        <v>821386.1</v>
+      </c>
+      <c r="X69" s="9">
+        <v>1323596.8</v>
+      </c>
+      <c r="Y69" s="9">
+        <v>202393.8</v>
+      </c>
+      <c r="Z69" s="9">
+        <v>54208.3</v>
+      </c>
+      <c r="AA69" s="9">
+        <v>209537.5</v>
+      </c>
+      <c r="AB69" s="9">
+        <v>12772617.699999999</v>
+      </c>
+      <c r="AC69" s="9">
+        <v>1324.8</v>
+      </c>
+      <c r="AD69" s="9">
+        <v>947.1</v>
+      </c>
+      <c r="AE69" s="9">
+        <v>1123.7</v>
+      </c>
+      <c r="AF69" s="9">
+        <v>973.1</v>
+      </c>
+      <c r="AG69" s="9">
+        <v>1103.5</v>
+      </c>
+      <c r="AH69" s="9">
+        <v>750.3</v>
+      </c>
+      <c r="AI69" s="9">
+        <v>597.29999999999995</v>
+      </c>
+      <c r="AJ69" s="9">
+        <v>1018</v>
+      </c>
+      <c r="AK69" s="9">
+        <v>1111.0999999999999</v>
+      </c>
+      <c r="AL69" s="9">
+        <v>3542</v>
+      </c>
+      <c r="AM69" s="9">
+        <v>3031.5</v>
+      </c>
+      <c r="AN69" s="9">
+        <v>2311.9</v>
+      </c>
+      <c r="AO69" s="9">
+        <v>844.1</v>
+      </c>
+      <c r="AP69" s="9">
+        <v>1199.4000000000001</v>
+      </c>
+      <c r="AQ69" s="9">
+        <v>269.8</v>
+      </c>
+      <c r="AR69" s="9">
+        <v>90.8</v>
+      </c>
+      <c r="AS69" s="9">
+        <v>205.8</v>
+      </c>
+      <c r="AT69" s="9">
+        <v>11495.2</v>
       </c>
     </row>
   </sheetData>
@@ -13985,7 +14099,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:Z11"/>
   <sheetFormatPr defaultColWidth="7.7109375" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -14054,22 +14168,22 @@
       </c>
     </row>
     <row r="6" spans="2:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
     </row>
     <row r="10" spans="2:26" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>109</v>
       </c>
     </row>
